--- a/event_registration_forms/046_event_rehearsal_scheduling_form--event_registration_forms.xlsx
+++ b/event_registration_forms/046_event_rehearsal_scheduling_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1364,29 +1364,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>event_rehearsal_form_9_choices</t>
+          <t>event_rehearsal_form_10_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1517,27 +1517,10 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>event_rehearsal_form_10_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
         <is>
           <t>20</t>
         </is>
